--- a/contenuti.xlsx
+++ b/contenuti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fulviomolinari/Documents/GitHub/Agifar Bari/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7E8860-9D9F-2D4D-A70B-1468EA6AB3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E1AE9-607E-CB47-866A-81E17DA9ECFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="154">
   <si>
     <t>Come aggiornare il sito Agifar BAT</t>
   </si>
@@ -483,6 +483,12 @@
   </si>
   <si>
     <t>La Salute in Piazza Modificato per testare il sito</t>
+  </si>
+  <si>
+    <t>Link modulo iscrizione</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSeqDxvKw52WBr8BWe44XtwaiBTJLB9gOOyKjIb7110QeC-pxQ/viewform?usp=header</t>
   </si>
 </sst>
 </file>
@@ -490,9 +496,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,37 +511,51 @@
       <sz val="14"/>
       <color rgb="FF3C6722"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF8E8A7F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -574,10 +594,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -591,13 +612,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -609,8 +630,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1710,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1803,52 +1828,50 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="1:3" ht="28" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="9"/>
-    </row>
-    <row r="12" spans="1:3" ht="56" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" ht="56" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>136</v>
@@ -1856,10 +1879,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>136</v>
@@ -1867,10 +1890,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>136</v>
@@ -1878,10 +1901,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>136</v>
@@ -1889,10 +1912,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>136</v>
@@ -1900,10 +1923,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>136</v>
@@ -1911,16 +1934,30 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>136</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{4E7897C9-B31F-E646-96FA-66230E5C51E0}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>